--- a/ig/DM-MARS-2026/CodeSystem-TRE-R213-ModePriseEnCharge.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-TRE-R213-ModePriseEnCharge.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,7 +556,7 @@
     <t>58</t>
   </si>
   <si>
-    <t>Coordination de parcours</t>
+    <t>Suivi ou coordination de parcours</t>
   </si>
   <si>
     <t>La coordination de parcours est un mode de prise en charge correspondant à l'appui à l'organisation des parcours complexes ou des parcours spécifiques à certaines pathologies.  Elle a pour objectif d'améliorer la fluidité des échanges entre les différents acteurs.</t>
